--- a/结果/问题三_覆盖核验_修复版.xlsx
+++ b/结果/问题三_覆盖核验_修复版.xlsx
@@ -450,13 +450,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -481,7 +481,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -509,7 +509,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -520,13 +520,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -537,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -551,7 +551,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -590,13 +590,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="b">
         <v>1</v>
       </c>
       <c r="D12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
@@ -635,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
